--- a/Assets/Art/Summon/Pic/PicList.xlsx
+++ b/Assets/Art/Summon/Pic/PicList.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84964FFC-7FC2-40DE-8B93-837D625018E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC4D234B-2F51-4D40-A771-C7CD48019164}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="143">
   <si>
     <t>01</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -539,6 +539,18 @@
   </si>
   <si>
     <t>若击败了敌方动物，则继续攻击</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>大象</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>蝎子</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>野猪</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1717,56 +1729,6 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>99131</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>27891</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>558966</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>464492</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="49" name="图片 48">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3E2AFB9C-6F30-A44C-7D53-33071E5E8CCC}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId23" cstate="print">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm flipH="1">
-          <a:off x="99131" y="11487199"/>
-          <a:ext cx="459835" cy="436601"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
       <xdr:colOff>62148</xdr:colOff>
       <xdr:row>24</xdr:row>
       <xdr:rowOff>24019</xdr:rowOff>
@@ -1791,7 +1753,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId24" cstate="print">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId23" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -1841,7 +1803,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId25" cstate="print">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId24" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -1891,7 +1853,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId26" cstate="print">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId25" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -1941,7 +1903,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId27" cstate="print">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId26" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -1991,7 +1953,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId28" cstate="print">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId27" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -2041,7 +2003,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId29" cstate="print">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId28" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -2067,56 +2029,6 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>197846</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>47690</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>533609</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>368056</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="63" name="图片 62">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{75543125-6D7F-C076-35B7-02A255ACA83A}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId30" cstate="print">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm flipH="1">
-          <a:off x="197846" y="12620690"/>
-          <a:ext cx="335763" cy="320366"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
       <xdr:colOff>31939</xdr:colOff>
       <xdr:row>31</xdr:row>
       <xdr:rowOff>60558</xdr:rowOff>
@@ -2141,7 +2053,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId31" cstate="print">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId29" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -2167,56 +2079,6 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>135077</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>102442</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>473893</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>431245</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="67" name="图片 66">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E3C1B77B-776E-8E20-5B50-46DCAF2C291B}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId32" cstate="print">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm flipH="1">
-          <a:off x="135077" y="13513642"/>
-          <a:ext cx="338816" cy="327489"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
       <xdr:colOff>73084</xdr:colOff>
       <xdr:row>33</xdr:row>
       <xdr:rowOff>56643</xdr:rowOff>
@@ -2241,7 +2103,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId33" cstate="print">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId30" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -2267,156 +2129,6 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>180434</xdr:colOff>
-      <xdr:row>34</xdr:row>
-      <xdr:rowOff>83810</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>526371</xdr:colOff>
-      <xdr:row>34</xdr:row>
-      <xdr:rowOff>404175</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="71" name="图片 70">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C0FFB897-18FB-A27A-0E3B-D1ACCD224EA3}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId34" cstate="print">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm flipH="1">
-          <a:off x="180434" y="14333210"/>
-          <a:ext cx="345937" cy="320365"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>91756</xdr:colOff>
-      <xdr:row>35</xdr:row>
-      <xdr:rowOff>36743</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>544809</xdr:colOff>
-      <xdr:row>35</xdr:row>
-      <xdr:rowOff>447054</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="73" name="图片 72">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AA9B29B6-83E2-C7F2-4590-B47CAC22F75F}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId35" cstate="print">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm flipH="1">
-          <a:off x="91756" y="14705243"/>
-          <a:ext cx="453053" cy="408997"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>119836</xdr:colOff>
-      <xdr:row>36</xdr:row>
-      <xdr:rowOff>34343</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>572889</xdr:colOff>
-      <xdr:row>36</xdr:row>
-      <xdr:rowOff>444653</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="75" name="图片 74">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A587CC70-9EB8-75F6-0E0C-F4A07657B99B}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId36" cstate="print">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm flipH="1">
-          <a:off x="119836" y="15121943"/>
-          <a:ext cx="453053" cy="408997"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
       <xdr:colOff>78374</xdr:colOff>
       <xdr:row>37</xdr:row>
       <xdr:rowOff>38249</xdr:rowOff>
@@ -2441,7 +2153,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId37" cstate="print">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId31" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -2491,7 +2203,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId38" cstate="print">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId32" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -2541,7 +2253,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId39" cstate="print">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId33" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -2556,6 +2268,356 @@
         <a:xfrm flipH="1">
           <a:off x="87311" y="19301319"/>
           <a:ext cx="434063" cy="412392"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>46893</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>36489</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>484984</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>452721</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="图片 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{28437D08-4AF1-6C43-75CC-FF4342D37BD3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId34" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="46893" y="11495797"/>
+          <a:ext cx="438091" cy="416232"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>79662</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>31881</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>504906</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>453253</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="8" name="图片 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{78A974AE-8CCB-9B3D-9175-202DE8E6BDEC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId35" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="79662" y="14978804"/>
+          <a:ext cx="425244" cy="421372"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>86586</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>46673</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>515684</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>461639</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="16" name="图片 15">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{27A53DAC-A3E7-88C9-6B83-20DA5CD74F2D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId36" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="86586" y="15990058"/>
+          <a:ext cx="429098" cy="414966"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>116955</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>54358</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>549907</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>452605</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="24" name="图片 23">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A5B0697A-70D7-FDF0-7753-D3BED2811BB7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId37" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="116955" y="16994204"/>
+          <a:ext cx="432952" cy="398247"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>71122</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>44012</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>502789</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>458959</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="30" name="图片 29">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EEF2086C-4A72-3235-BC16-21B7DD031A9D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId38" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="71122" y="17980320"/>
+          <a:ext cx="431667" cy="414947"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>58617</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>17585</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>530223</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>483576</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="34" name="图片 33">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BBCA7E15-6E34-BED0-264C-C62A3ED9EF45}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId39" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="58617" y="5498123"/>
+          <a:ext cx="471606" cy="465991"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>134815</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>46890</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>571621</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>450276</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="36" name="图片 35">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{825B73F0-E72D-4C3A-B63E-60D9B65CF0D9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId40" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="134815" y="17484967"/>
+          <a:ext cx="436806" cy="403386"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3075,6 +3137,9 @@
       <c r="B12" s="1" t="s">
         <v>11</v>
       </c>
+      <c r="C12" s="1" t="s">
+        <v>140</v>
+      </c>
       <c r="D12" t="s">
         <v>112</v>
       </c>
@@ -3276,6 +3341,9 @@
       <c r="B24" s="1" t="s">
         <v>22</v>
       </c>
+      <c r="C24" s="1" t="s">
+        <v>141</v>
+      </c>
       <c r="D24" t="s">
         <v>127</v>
       </c>
@@ -3493,6 +3561,9 @@
     <row r="37" spans="2:6" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B37" s="1" t="s">
         <v>73</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>142</v>
       </c>
       <c r="D37" t="s">
         <v>115</v>

--- a/Assets/Art/Summon/Pic/PicList.xlsx
+++ b/Assets/Art/Summon/Pic/PicList.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC4D234B-2F51-4D40-A771-C7CD48019164}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A20716A6-8161-4C80-8286-8E5C36FD420C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -351,10 +351,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>你的防御力锁定为零，但是拥有三点生命值。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>4-1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -370,10 +366,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>被击败时，进入无敌状态，再进行你的回合两次之后死亡（期间再次被击败时直接死亡）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>当你或左右两侧受到命中己方法师的攻击时，你可以选择为其承受攻击</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -494,30 +486,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>攻击时，立即恢复一点生命值</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>打出时，立即恢复一点生命值</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>死亡时，立即恢复一点生命值</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>死亡时，攻击力最高的敌人死亡</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>打出时，选择一个攻击力小于你的敌人立即死亡</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>打出时，会使面前的敌人立即死亡</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>死亡时，会使面前的敌人立即死亡</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -551,6 +523,34 @@
   </si>
   <si>
     <t>野猪</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>‌打出时，所有防御力为一的敌人立即死亡</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>‌打出时，若面前的敌人的攻击力小于你，则其立即死亡</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>死亡时，己方法师立即恢复一点生命值</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>‌打出时，己方法师立即恢复一点生命值</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>‌打出时，己方法师的生命值可以变为 对方法师的生命值减一</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>你的防御力锁定为零，但是拥有三点生命值</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>被击败时进入无敌，再进行你的回合两次之后死亡（期间再次被击败直接死亡）</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2943,7 +2943,9 @@
   <cols>
     <col min="2" max="3" width="8.88671875" style="1"/>
     <col min="4" max="4" width="78.5546875" customWidth="1"/>
-    <col min="5" max="8" width="8.88671875" style="1"/>
+    <col min="5" max="6" width="8.88671875" style="1"/>
+    <col min="7" max="7" width="41.21875" style="1" customWidth="1"/>
+    <col min="8" max="8" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:6" ht="39" customHeight="1" x14ac:dyDescent="0.25">
@@ -2960,7 +2962,7 @@
         <v>91</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
     </row>
     <row r="2" spans="2:6" ht="39" customHeight="1" x14ac:dyDescent="0.25">
@@ -2971,13 +2973,13 @@
         <v>39</v>
       </c>
       <c r="D2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
     </row>
     <row r="3" spans="2:6" ht="39" customHeight="1" x14ac:dyDescent="0.25">
@@ -2988,13 +2990,13 @@
         <v>40</v>
       </c>
       <c r="D3" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
     </row>
     <row r="4" spans="2:6" ht="39" customHeight="1" x14ac:dyDescent="0.25">
@@ -3005,13 +3007,13 @@
         <v>41</v>
       </c>
       <c r="D4" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
     </row>
     <row r="5" spans="2:6" ht="39" customHeight="1" x14ac:dyDescent="0.25">
@@ -3022,13 +3024,13 @@
         <v>42</v>
       </c>
       <c r="D5" t="s">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>123</v>
+        <v>92</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
     </row>
     <row r="6" spans="2:6" ht="39" customHeight="1" x14ac:dyDescent="0.25">
@@ -3039,13 +3041,13 @@
         <v>46</v>
       </c>
       <c r="D6" t="s">
-        <v>105</v>
+        <v>79</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
     </row>
     <row r="7" spans="2:6" ht="39" customHeight="1" x14ac:dyDescent="0.25">
@@ -3056,13 +3058,13 @@
         <v>45</v>
       </c>
       <c r="D7" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
     </row>
     <row r="8" spans="2:6" ht="39" customHeight="1" x14ac:dyDescent="0.25">
@@ -3073,13 +3075,13 @@
         <v>44</v>
       </c>
       <c r="D8" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
     </row>
     <row r="9" spans="2:6" ht="39" customHeight="1" x14ac:dyDescent="0.25">
@@ -3090,13 +3092,13 @@
         <v>43</v>
       </c>
       <c r="D9" t="s">
-        <v>79</v>
+        <v>103</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>80</v>
+        <v>118</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
     </row>
     <row r="10" spans="2:6" ht="39" customHeight="1" x14ac:dyDescent="0.25">
@@ -3107,13 +3109,13 @@
         <v>47</v>
       </c>
       <c r="D10" t="s">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
     </row>
     <row r="11" spans="2:6" ht="39" customHeight="1" x14ac:dyDescent="0.25">
@@ -3124,13 +3126,13 @@
         <v>49</v>
       </c>
       <c r="D11" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
     </row>
     <row r="12" spans="2:6" ht="39" customHeight="1" x14ac:dyDescent="0.25">
@@ -3138,16 +3140,16 @@
         <v>11</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="D12" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
     </row>
     <row r="13" spans="2:6" ht="39" customHeight="1" x14ac:dyDescent="0.25">
@@ -3158,13 +3160,13 @@
         <v>50</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
     </row>
     <row r="14" spans="2:6" ht="39" customHeight="1" x14ac:dyDescent="0.25">
@@ -3175,13 +3177,13 @@
         <v>51</v>
       </c>
       <c r="D14" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
     </row>
     <row r="15" spans="2:6" ht="39" customHeight="1" x14ac:dyDescent="0.25">
@@ -3192,13 +3194,13 @@
         <v>52</v>
       </c>
       <c r="D15" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
     </row>
     <row r="16" spans="2:6" ht="39" customHeight="1" x14ac:dyDescent="0.25">
@@ -3215,7 +3217,7 @@
         <v>78</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
     </row>
     <row r="17" spans="2:6" ht="39" customHeight="1" x14ac:dyDescent="0.25">
@@ -3226,13 +3228,13 @@
         <v>54</v>
       </c>
       <c r="D17" t="s">
-        <v>85</v>
+        <v>139</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
     </row>
     <row r="18" spans="2:6" ht="39" customHeight="1" x14ac:dyDescent="0.25">
@@ -3249,7 +3251,7 @@
         <v>84</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
     </row>
     <row r="19" spans="2:6" ht="39" customHeight="1" x14ac:dyDescent="0.25">
@@ -3260,13 +3262,13 @@
         <v>56</v>
       </c>
       <c r="D19" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>78</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
     </row>
     <row r="20" spans="2:6" ht="39" customHeight="1" x14ac:dyDescent="0.25">
@@ -3277,13 +3279,13 @@
         <v>57</v>
       </c>
       <c r="D20" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="E20" s="1" t="s">
         <v>91</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
     </row>
     <row r="21" spans="2:6" ht="39" customHeight="1" x14ac:dyDescent="0.25">
@@ -3294,13 +3296,13 @@
         <v>58</v>
       </c>
       <c r="D21" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
     </row>
     <row r="22" spans="2:6" ht="39" customHeight="1" x14ac:dyDescent="0.25">
@@ -3311,13 +3313,13 @@
         <v>59</v>
       </c>
       <c r="D22" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
     </row>
     <row r="23" spans="2:6" ht="39" customHeight="1" x14ac:dyDescent="0.25">
@@ -3334,7 +3336,7 @@
         <v>86</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
     </row>
     <row r="24" spans="2:6" ht="39" customHeight="1" x14ac:dyDescent="0.25">
@@ -3342,16 +3344,16 @@
         <v>22</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="D24" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
     </row>
     <row r="25" spans="2:6" ht="39" customHeight="1" x14ac:dyDescent="0.25">
@@ -3362,13 +3364,13 @@
         <v>61</v>
       </c>
       <c r="D25" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
     </row>
     <row r="26" spans="2:6" ht="39" customHeight="1" x14ac:dyDescent="0.25">
@@ -3379,13 +3381,13 @@
         <v>62</v>
       </c>
       <c r="D26" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>88</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
     </row>
     <row r="27" spans="2:6" ht="39" customHeight="1" x14ac:dyDescent="0.25">
@@ -3396,13 +3398,13 @@
         <v>63</v>
       </c>
       <c r="D27" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
     </row>
     <row r="28" spans="2:6" ht="39" customHeight="1" x14ac:dyDescent="0.25">
@@ -3413,13 +3415,13 @@
         <v>64</v>
       </c>
       <c r="D28" t="s">
-        <v>97</v>
+        <v>142</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
     </row>
     <row r="29" spans="2:6" ht="39" customHeight="1" x14ac:dyDescent="0.25">
@@ -3433,10 +3435,10 @@
         <v>119</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>120</v>
+        <v>91</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
     </row>
     <row r="30" spans="2:6" ht="39" customHeight="1" x14ac:dyDescent="0.25">
@@ -3453,7 +3455,7 @@
         <v>82</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
     </row>
     <row r="31" spans="2:6" ht="39" customHeight="1" x14ac:dyDescent="0.25">
@@ -3464,13 +3466,13 @@
         <v>67</v>
       </c>
       <c r="D31" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
     </row>
     <row r="32" spans="2:6" ht="39" customHeight="1" x14ac:dyDescent="0.25">
@@ -3481,13 +3483,13 @@
         <v>68</v>
       </c>
       <c r="D32" t="s">
-        <v>89</v>
+        <v>136</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
     </row>
     <row r="33" spans="2:6" ht="39" customHeight="1" x14ac:dyDescent="0.25">
@@ -3498,13 +3500,13 @@
         <v>69</v>
       </c>
       <c r="D33" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
     </row>
     <row r="34" spans="2:6" ht="39" customHeight="1" x14ac:dyDescent="0.25">
@@ -3515,13 +3517,13 @@
         <v>70</v>
       </c>
       <c r="D34" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
     </row>
     <row r="35" spans="2:6" ht="39" customHeight="1" x14ac:dyDescent="0.25">
@@ -3532,13 +3534,13 @@
         <v>71</v>
       </c>
       <c r="D35" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
     </row>
     <row r="36" spans="2:6" ht="39" customHeight="1" x14ac:dyDescent="0.25">
@@ -3548,14 +3550,14 @@
       <c r="C36" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D36" s="1" t="s">
-        <v>134</v>
+      <c r="D36" t="s">
+        <v>138</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
     </row>
     <row r="37" spans="2:6" ht="39" customHeight="1" x14ac:dyDescent="0.25">
@@ -3563,16 +3565,16 @@
         <v>73</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="D37" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>91</v>
+        <v>121</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
     </row>
     <row r="38" spans="2:6" ht="39" customHeight="1" x14ac:dyDescent="0.25">
@@ -3582,14 +3584,14 @@
       <c r="C38" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="D38" t="s">
-        <v>133</v>
+      <c r="D38" s="1" t="s">
+        <v>127</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
     </row>
     <row r="39" spans="2:6" ht="39" customHeight="1" x14ac:dyDescent="0.25">
@@ -3600,13 +3602,13 @@
         <v>75</v>
       </c>
       <c r="D39" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
     </row>
     <row r="40" spans="2:6" ht="39" customHeight="1" x14ac:dyDescent="0.25">
@@ -3617,13 +3619,13 @@
         <v>76</v>
       </c>
       <c r="D40" t="s">
+        <v>85</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="F40" s="1" t="s">
         <v>129</v>
-      </c>
-      <c r="E40" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="F40" s="1" t="s">
-        <v>136</v>
       </c>
     </row>
   </sheetData>
